--- a/Q3_05-08-2026_Excel_Zapyt_na_komertsiinu_propozytsiiu.xlsx
+++ b/Q3_05-08-2026_Excel_Zapyt_na_komertsiinu_propozytsiiu.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\xll_dropper\xll_dropper_v5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Programs\xll_dropper\Anti_MOTW_Dropper (exe)\ZIP-Telegram-MOTW3\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7597202-CA2A-4072-8778-4B2A800298D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F5F786-FB66-4CBE-88B5-4A5FC60183D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25845" windowHeight="12045" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="19200" windowHeight="8535" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Запит позицій" sheetId="1" r:id="rId1"/>
@@ -33,9 +33,6 @@
     <t>Дата формування:</t>
   </si>
   <si>
-    <t>03.08.2026</t>
-  </si>
-  <si>
     <t>Умови оплати:</t>
   </si>
   <si>
@@ -163,6 +160,9 @@
     <t>Модель Nomad Dual Band, версія ISM2.4/FCC915, мікроконтролери ESP32 та ESP32-C3, RF-чипи Semtech LR1121 ×2, частоти 2400–2479 МГц / 903–927 МГц, оновлення 50–500 Гц (до 1000 Гц у V3.5), Wi-Fi та Bluetooth, RGB-підсвічування, роз’єми 5-pin Micro та 8-pin Nano, живлення XT30 6–16,8 В.
 Розміри: приблизно 125 × 65 × 35 мм
 Вага: приблизно 150 г</t>
+  </si>
+  <si>
+    <t>08.08.2026</t>
   </si>
 </sst>
 </file>
@@ -694,7 +694,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="C3" s="10"/>
       <c r="D3" s="10"/>
@@ -706,10 +706,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
         <v>3</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>4</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
@@ -721,10 +721,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="s">
         <v>5</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -736,10 +736,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>8</v>
       </c>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
@@ -751,31 +751,31 @@
     </row>
     <row r="8" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="96" customHeight="1" x14ac:dyDescent="0.25">
@@ -783,13 +783,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>19</v>
       </c>
       <c r="E9" s="5">
         <v>3</v>
@@ -804,13 +804,13 @@
         <v>2</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="8">
         <v>3</v>
@@ -825,13 +825,13 @@
         <v>3</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="5">
         <v>4</v>
@@ -846,13 +846,13 @@
         <v>4</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E12" s="8">
         <v>3</v>
@@ -867,13 +867,13 @@
         <v>5</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="5">
         <v>5</v>
@@ -888,13 +888,13 @@
         <v>6</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="8">
         <v>5</v>
@@ -909,13 +909,13 @@
         <v>7</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="5">
         <v>5</v>
@@ -930,13 +930,13 @@
         <v>8</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="E16" s="8">
         <v>3</v>
@@ -951,13 +951,13 @@
         <v>9</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E17" s="5">
         <v>5</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="20" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B20" s="10"/>
       <c r="C20" s="10"/>
@@ -982,7 +982,7 @@
     </row>
     <row r="21" spans="1:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="10"/>
       <c r="C21" s="10"/>
